--- a/output/2026-10-05_17_Croazia_Dubrovacko-neretvanska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-05_17_Croazia_Dubrovacko-neretvanska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore/service di utensileria elettrica e pneumatica professionale (Bosch, Metabo, Makita, Flex, Dremel, Proxxon) e attrezzature per saldatura/officina (saldatrici Telwin, compressori Comet, generatori Powermate/Pramac). Verificato tramite piu' fonti indipendenti (sito aziendale, nicelocal.com.hr, croatiayp.com).</t>
+          <t>Rivenditore/service di utensileria elettrica e pneumatica professionale (Bosch, Metabo, Makita, Flex, Dremel, Proxxon) e attrezzature per saldatura/officina (saldatrici Telwin, compressori Comet, generatori Powermate/Pramac). Verificato tramite piu' fonti indipendenti (sito aziendale, nicelocal.com.hr, croatiayp.com). [DUPLICATO — vedi anche: 2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
